--- a/data/trans_orig/IP22C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP22C-Habitat-trans_orig.xlsx
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24798</t>
+          <t>24583</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48688</t>
+          <t>48555</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32260</t>
+          <t>32214</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37365</t>
+          <t>37358</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42824</t>
+          <t>42743</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50105</t>
+          <t>50093</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>78139</t>
+          <t>77712</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>86721</t>
+          <t>86751</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>642</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9164</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11739</t>
+          <t>12374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29935</t>
+          <t>29871</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34884</t>
+          <t>34885</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34248</t>
+          <t>34167</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65770</t>
+          <t>66512</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72377</t>
+          <t>72356</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19527</t>
+          <t>20186</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28339</t>
+          <t>28356</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50981</t>
+          <t>50187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58066</t>
+          <t>58085</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>695</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4705</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>114183</t>
+          <t>114541</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>122533</t>
+          <t>122677</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>135007</t>
+          <t>134622</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>145086</t>
+          <t>144948</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>252111</t>
+          <t>252863</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>265067</t>
+          <t>265583</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>13893</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21503</t>
+          <t>21213</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23748</t>
+          <t>23840</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29642</t>
+          <t>29653</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32988</t>
+          <t>33459</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37845</t>
+          <t>37843</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60363</t>
+          <t>59473</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67203</t>
+          <t>66917</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>684</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8446</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46620</t>
+          <t>46929</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53962</t>
+          <t>53977</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50706</t>
+          <t>50866</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57724</t>
+          <t>57711</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>99643</t>
+          <t>100047</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>110466</t>
+          <t>110191</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9904</t>
+          <t>9595</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17226</t>
+          <t>16822</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27755</t>
+          <t>27801</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50032</t>
+          <t>50229</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56955</t>
+          <t>56909</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79998</t>
+          <t>79664</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87447</t>
+          <t>87439</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33102</t>
+          <t>33447</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37943</t>
+          <t>37819</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43610</t>
+          <t>43596</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73419</t>
+          <t>73313</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79857</t>
+          <t>79855</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>737</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1382</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>139332</t>
+          <t>139443</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>149934</t>
+          <t>149415</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>180640</t>
+          <t>180717</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>192555</t>
+          <t>192807</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>324109</t>
+          <t>323174</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>340040</t>
+          <t>340153</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>15460</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9971</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21886</t>
+          <t>21809</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17389</t>
+          <t>17276</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33320</t>
+          <t>34255</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -5757,62 +5757,62 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4808</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18,47%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1681</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4360</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4886</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7,2%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,74%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1681</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5474</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7521</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19265</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24851</t>
+          <t>24864</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12931</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>20410</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35009</t>
+          <t>34942</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43980</t>
+          <t>44091</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10761</t>
+          <t>10522</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25909</t>
+          <t>25403</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32242</t>
+          <t>32282</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,47 +6341,47 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>94,0%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>30740</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>27967</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>32121</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
           <t>93,88%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>30740</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>27412</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>32125</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>93,88%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>55855</t>
+          <t>56011</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>63910</t>
+          <t>63721</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>8158</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>10137</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28967</t>
+          <t>28836</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32579</t>
+          <t>32573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23766</t>
+          <t>23040</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>28113</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54680</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60226</t>
+          <t>60168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -6900,7 +6900,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5996</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,03%</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17461</t>
+          <t>16581</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18297</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24545</t>
+          <t>24500</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38643</t>
+          <t>37698</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46233</t>
+          <t>46234</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>778</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6907</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>99191</t>
+          <t>99877</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>109309</t>
+          <t>109689</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>90401</t>
+          <t>90483</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>101999</t>
+          <t>102156</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>193632</t>
+          <t>193585</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>209572</t>
+          <t>208802</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11433</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25848</t>
+          <t>24999</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>15954</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16342</t>
+          <t>15972</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35156</t>
+          <t>35078</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40641</t>
+          <t>40666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>512</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8815,7 +8815,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27650</t>
+          <t>27323</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33935</t>
+          <t>33635</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24763</t>
+          <t>25419</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31073</t>
+          <t>30993</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>54588</t>
+          <t>55295</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>63531</t>
+          <t>63387</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6697</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>775</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>10770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>6412</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>727</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18473</t>
+          <t>18676</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24051</t>
+          <t>24048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18206</t>
+          <t>18646</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24894</t>
+          <t>24856</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39571</t>
+          <t>40308</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48112</t>
+          <t>48424</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>784</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7687</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13712</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25023</t>
+          <t>25440</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32032</t>
+          <t>32024</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41340</t>
+          <t>40851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48183</t>
+          <t>48518</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9868,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3410</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>929</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7930</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>735</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>83094</t>
+          <t>82879</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>92466</t>
+          <t>92389</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>95364</t>
+          <t>94476</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>106112</t>
+          <t>106010</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>182002</t>
+          <t>181580</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>196902</t>
+          <t>196510</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8562</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>22112</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22C-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP22C-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24254</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>27171</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24583</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24815</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>27747</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,92%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,6%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>89,43%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24254</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>74</t>
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48555</t>
+          <t>48702</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,107 +949,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>576</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3164</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2932</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2,08%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>10,57%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>3299</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>3446</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -1062,57 +1062,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24254</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24254</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24254</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>27747</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>27747</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>27747</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>24254</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>24254</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>24254</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1179,107 +1179,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>680</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3696</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3756</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4080</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1292,72 +1292,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47395</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>43298</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>50156</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>89,92%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>82,15%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>95,16%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>35447</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>32214</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>37358</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>32311</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>37360</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>93,28%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>84,77%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>98,31%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>47395</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>42743</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>50093</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>89,92%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>77712</t>
+          <t>77631</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>86751</t>
+          <t>86787</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -1405,72 +1405,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4632</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8699</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,79%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2553</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5786</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,72%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4632</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8620</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>12377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -1518,57 +1518,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>52707</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>52707</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>52707</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>38000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>38000</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>38000</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>52707</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>52707</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>52707</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1748,72 +1748,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36980</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34722</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>38110</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>91,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>33140</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29871</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34885</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>30177</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>34928</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>93,23%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>84,03%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>98,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>36980</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>34167</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>38110</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66512</t>
+          <t>66398</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72356</t>
+          <t>72270</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -1861,72 +1861,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3388</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2406</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5675</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5369</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>6,77%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,97%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1130</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3943</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -1974,57 +1974,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38110</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38110</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38110</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>35546</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38110</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38110</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38110</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2096,102 +2096,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3413</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,66%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>778</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3469</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4091</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,13%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>13,93%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>16,43%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1457</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3589</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4912</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1457</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4944</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -2204,74 +2204,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>31915</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>28391</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33985</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>80,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,22%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>23390</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>20186</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>20275</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>24902</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>93,93%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>81,06%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>81,42%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>31915</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>28356</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>33989</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,37%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>80,29%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>78</t>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50187</t>
+          <t>51071</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58085</t>
+          <t>58185</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -2317,72 +2317,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2724</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6154</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7,71%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>17,42%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>733</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3029</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4391</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>2,95%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>12,16%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2724</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>6126</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7569</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -2430,57 +2430,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>35318</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>35318</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>35318</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>24902</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>24902</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>24902</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>35318</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>35318</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>35318</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2547,72 +2547,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4786</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>778</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4655</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3663</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4735</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -2660,72 +2660,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>140545</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>135232</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>144965</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>93,45%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>89,92%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>96,39%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>119149</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>114541</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>122677</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>114370</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>122457</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>94,42%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>90,76%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>140545</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>134622</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>144948</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>93,45%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>252863</t>
+          <t>252379</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>265583</t>
+          <t>265372</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -2773,72 +2773,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8486</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4663</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>13694</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>6268</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2915</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>10609</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>3163</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>10830</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>4,97%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>8486</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>4469</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>13893</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21213</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -2886,57 +2886,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>150389</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>150389</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>150389</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>126195</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>126195</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>126195</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>150389</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>150389</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>150389</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3067,7 +3067,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3348,72 +3348,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>36500</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33101</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>37845</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,87%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,04%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>27855</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23840</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29653</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24174</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>29663</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>91,82%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>78,58%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>36500</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>33459</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>37843</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,87%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59473</t>
+          <t>59536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66917</t>
+          <t>67214</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -3466,67 +3466,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5371</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>13,96%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>2482</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6497</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6163</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>8,18%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>21,42%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1972</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>629</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5013</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -3574,57 +3574,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>38472</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>38472</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>38472</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>30337</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>30337</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>30337</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>38472</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>38472</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>38472</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3804,72 +3804,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>54968</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50733</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>57691</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>91,09%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>84,07%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>95,6%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51177</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>46929</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>53977</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>46874</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>53936</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>90,54%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>83,03%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>54968</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>50866</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>57711</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>91,09%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>100047</t>
+          <t>100158</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>110191</t>
+          <t>110228</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -3922,67 +3922,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>5377</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9612</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,93%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>5347</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2547</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9595</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2588</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9650</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,46%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5377</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9479</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,91%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16822</t>
+          <t>16711</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -4030,57 +4030,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>60345</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>60345</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>60345</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>56524</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>56524</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>56524</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>60345</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>60345</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>60345</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4260,74 +4260,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54395</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>50298</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>56915</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>91,61%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>84,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>95,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>30461</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>27801</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>27731</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>31136</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>97,83%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>89,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>89,06%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>54395</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>50229</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>56909</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>91,61%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>84,59%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>95,85%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>130</t>
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79664</t>
+          <t>80408</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87439</t>
+          <t>87438</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4373,72 +4373,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4981</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2461</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9078</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>675</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3335</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2,17%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4981</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9147</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -4486,57 +4486,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>59376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>59376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>59376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>31136</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>31136</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>31136</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>59376</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>59376</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>59376</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4716,74 +4716,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>41456</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>37729</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>43586</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>85,1%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,32%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>36172</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>33447</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>32949</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>36906</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,01%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,63%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>89,28%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>41456</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>37819</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>43596</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,51%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>85,31%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>104</t>
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73313</t>
+          <t>72455</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79855</t>
+          <t>79809</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -4829,72 +4829,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2877</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6604</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>14,9%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>734</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3459</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3957</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>1,99%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,37%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2877</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>737</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>6514</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -4942,57 +4942,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>44333</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>44333</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>44333</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>36906</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>36906</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>36906</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>44333</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>44333</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>44333</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5172,72 +5172,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>187320</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>180590</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>192767</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>92,49%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>89,17%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>95,18%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>145664</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>139443</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>149415</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>139157</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>149578</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>94,04%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>90,02%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>96,46%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>187320</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>180717</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>192807</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>92,49%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>323174</t>
+          <t>324787</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>340153</t>
+          <t>339929</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -5285,72 +5285,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>15206</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9759</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>21936</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>7,51%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>10,83%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>9239</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>5488</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>15460</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>5325</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>15746</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>5,96%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>15206</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>9719</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>21809</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>7,51%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>17500</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34255</t>
+          <t>32642</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -5398,57 +5398,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>202526</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>202526</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>202526</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>154903</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>154903</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>154903</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>202526</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>202526</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>202526</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5568,7 +5568,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5579,7 +5579,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5747,72 +5747,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1681</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5618</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,2%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1793</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4808</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4789</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,89%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1681</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4886</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -5860,72 +5860,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17128</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12838</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20230</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>73,4%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>55,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>86,69%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22898</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19244</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24864</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19231</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24841</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>87,95%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>73,91%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,5%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17128</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12405</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20410</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>73,4%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34942</t>
+          <t>34813</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44091</t>
+          <t>44192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -5973,72 +5973,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8713</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>19,4%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>8,58%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>37,34%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1344</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4949</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4233</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>5,16%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,01%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4526</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1959</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>19,4%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10522</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -6086,57 +6086,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23335</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>23335</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23335</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>26036</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>26036</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>26036</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>23335</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>23335</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>23335</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6203,107 +6203,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>608</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3251</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3096</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,77%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3092</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3330</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -6316,72 +6316,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>30740</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>26699</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>32124</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>93,88%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>81,54%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>29841</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>25403</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>32282</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>25702</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>32449</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>86,89%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>73,97%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>94,0%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>30740</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>27967</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>32121</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>93,88%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>56011</t>
+          <t>55799</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>63721</t>
+          <t>63960</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -6429,72 +6429,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6046</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,12%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,46%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3894</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1755</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8158</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8036</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,34%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,75%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4778</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>10502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -6542,57 +6542,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32745</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>32745</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>32745</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>34343</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>34343</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>34343</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>32745</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>32745</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>32745</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6659,107 +6659,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>1003</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3152</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3020</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>3,03%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>9,14%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>3092</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>3540</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -6772,74 +6772,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>26782</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>23939</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>28128</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>93,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>83,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>31497</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>28836</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>32573</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>29106</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>32572</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>95,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>87,28%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>88,1%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>98,59%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>26782</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>23040</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>28113</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>93,44%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>80,38%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>98,08%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>93</t>
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>54694</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60168</t>
+          <t>60205</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -6885,72 +6885,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1882</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4725</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>540</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2958</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2704</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1882</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5624</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -6998,57 +6998,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>28664</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>28664</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>28664</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>33039</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>33039</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>33039</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>28664</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>28664</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>28664</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7120,102 +7120,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3313</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>846</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4683</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4156</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,75%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>18,43%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1587</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3844</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5131</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>14,81%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5837</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -7233,69 +7233,69 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>22244</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17919</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>24484</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>85,66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>69,01%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,29%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>20950</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>16581</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>17024</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>22549</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>92,91%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>73,53%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>75,5%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>22244</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>17986</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>24500</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>85,66%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>69,27%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>94,35%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>62</t>
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37698</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46234</t>
+          <t>46240</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -7341,72 +7341,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2982</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6696</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>11,48%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>25,78%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>753</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4109</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3993</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>3,34%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,22%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2982</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>778</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>6653</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>11,48%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -7454,57 +7454,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>25967</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>25967</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>25967</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>22549</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>22549</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>22549</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>25967</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>25967</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>25967</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7571,72 +7571,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7461</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>6,74%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>4250</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1741</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8205</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>8341</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>3,66%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2421</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>7361</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -7684,72 +7684,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>96894</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>89766</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>101783</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>87,52%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>81,08%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>91,94%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>105187</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>99877</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>109689</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>99708</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>109629</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>90,7%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>86,12%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>94,59%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>96894</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>90483</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>102156</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>87,52%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>193585</t>
+          <t>193205</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>208802</t>
+          <t>208934</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,17%</t>
         </is>
       </c>
     </row>
@@ -7797,72 +7797,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11395</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>7020</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>17946</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>10,29%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>16,21%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>6531</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3265</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>11257</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>3208</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>11392</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>5,63%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>11395</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>6774</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>17562</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>12242</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24999</t>
+          <t>26359</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -7910,57 +7910,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>110711</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>110711</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>110711</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>115968</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>115968</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>115968</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>110711</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>110711</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>110711</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -8091,7 +8091,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -8372,74 +8372,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17861</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14994</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18813</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,94%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>79,7%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>18908</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15954</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20009</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>94,5%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>79,73%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>18494</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15719</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19639</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>94,17%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>80,04%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20166</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15972</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21169</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>75,45%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>56</t>
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>39075</t>
+          <t>36354</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35078</t>
+          <t>32739</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40666</t>
+          <t>37907</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -8485,72 +8485,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>952</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3819</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20,3%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4055</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3920</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,27%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5197</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>512</t>
+          <t>545</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -8598,57 +8598,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18813</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18813</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18813</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>20009</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>20009</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20009</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>19639</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>19639</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21169</t>
+          <t>19639</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>41178</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41178</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41178</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8715,107 +8715,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2896</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2156</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,32%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>7,56%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>2252</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -8828,72 +8828,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>26740</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>23316</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>28552</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>91,68%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>79,94%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>97,89%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>31427</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>27323</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>33635</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>90,31%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>78,52%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>96,66%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29102</t>
+          <t>25213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25419</t>
+          <t>21507</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30993</t>
+          <t>27309</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>60529</t>
+          <t>51954</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>55295</t>
+          <t>46694</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>63387</t>
+          <t>54947</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -8941,72 +8941,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2427</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5851</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>20,06%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2880</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>816</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6825</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>796</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10770</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -9054,57 +9054,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29167</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29167</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>29167</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>34798</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>34798</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>34798</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31768</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31768</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31768</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>66566</t>
+          <t>57681</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66566</t>
+          <t>57681</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66566</t>
+          <t>57681</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9171,72 +9171,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3426</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,58%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>819</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4075</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4191</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,41%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>6412</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>498</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -9284,72 +9284,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>21518</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17817</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23012</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>91,56%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>75,82%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>97,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>22387</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18676</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>24048</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>90,13%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>75,19%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>96,82%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22799</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18646</t>
+          <t>19632</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24856</t>
+          <t>25006</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>45186</t>
+          <t>44780</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40308</t>
+          <t>40238</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48424</t>
+          <t>47380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -9397,72 +9397,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5595</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>23,81%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1632</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1567</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5141</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5390</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4141</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -9510,57 +9510,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>23501</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>23501</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>23501</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>24838</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>24838</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>24838</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25632</t>
+          <t>25695</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25632</t>
+          <t>25695</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25632</t>
+          <t>25695</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>50470</t>
+          <t>49196</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>50470</t>
+          <t>49196</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>50470</t>
+          <t>49196</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9740,74 +9740,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26544</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21958</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>28613</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>74,3%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>16130</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13342</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>16752</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>96,29%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>79,65%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>14355</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>11994</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>14966</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>95,92%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>80,14%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>29620</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>25440</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>32024</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>89,89%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>77,2%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>97,18%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>62</t>
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>45750</t>
+          <t>40900</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40851</t>
+          <t>36732</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48518</t>
+          <t>43484</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -9853,72 +9853,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>7594</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>25,7%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3410</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,71%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2972</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>20,35%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3333</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>7513</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>3619</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -9966,57 +9966,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>29552</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>29552</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>29552</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>16752</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>16752</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>16752</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32953</t>
+          <t>14966</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32953</t>
+          <t>14966</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32953</t>
+          <t>14966</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>49705</t>
+          <t>44519</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49705</t>
+          <t>44519</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49705</t>
+          <t>44519</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>3377</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6672</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>868</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>88853</t>
+          <t>92664</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>82879</t>
+          <t>86230</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>92389</t>
+          <t>96386</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>101687</t>
+          <t>81324</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>94476</t>
+          <t>75708</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>106010</t>
+          <t>84839</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>190540</t>
+          <t>173987</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>181580</t>
+          <t>166324</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>196510</t>
+          <t>180012</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>7331</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14192</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8997</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>20423</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>96398</t>
+          <t>101034</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>96398</t>
+          <t>101034</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>96398</t>
+          <t>101034</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>111522</t>
+          <t>88813</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>111522</t>
+          <t>88813</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>111522</t>
+          <t>88813</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>207919</t>
+          <t>189847</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>207919</t>
+          <t>189847</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>207919</t>
+          <t>189847</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
